--- a/Dekauto.Export.Service/Templates/diploma_supplement/saratov/bachelor_2_page.xlsx
+++ b/Dekauto.Export.Service/Templates/diploma_supplement/saratov/bachelor_2_page.xlsx
@@ -2001,7 +2001,7 @@
       <c r="H10" s="3"/>
     </row>
   </sheetData>
-  <sheetProtection password="DBF4" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection objects="1" password="DBF4" scenarios="1" sheet="1"/>
   <mergeCells count="2">
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="C8:D8"/>
@@ -2269,7 +2269,7 @@
       <c r="F21" s="3"/>
     </row>
   </sheetData>
-  <sheetProtection password="DBF4" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection objects="1" password="DBF4" scenarios="1" sheet="1"/>
   <mergeCells count="5">
     <mergeCell ref="C2:E2"/>
     <mergeCell ref="C1:E1"/>
@@ -4567,7 +4567,7 @@
       <c r="F135" s="3"/>
     </row>
   </sheetData>
-  <sheetProtection password="DBF4" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection objects="1" password="DBF4" scenarios="1" sheet="1"/>
   <conditionalFormatting sqref="E2:E134">
     <cfRule type="cellIs" dxfId="6" priority="2" operator="greaterThan">
       <formula>75</formula>
@@ -5306,7 +5306,7 @@
       <c r="E14" s="94"/>
     </row>
   </sheetData>
-  <sheetProtection password="DBF4" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection objects="1" password="DBF4" scenarios="1" sheet="1"/>
   <conditionalFormatting sqref="D2">
     <cfRule type="cellIs" dxfId="3" priority="8" operator="greaterThan">
       <formula>118</formula>
@@ -24215,7 +24215,7 @@
       <c r="DF167" s="29"/>
     </row>
   </sheetData>
-  <sheetProtection password="DBF4" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection objects="1" password="DBF4" scenarios="1" sheet="1"/>
   <mergeCells count="53">
     <mergeCell ref="C88:AZ90"/>
     <mergeCell ref="C73:AZ75"/>
@@ -30299,7 +30299,7 @@
       <c r="BC84" s="28"/>
     </row>
   </sheetData>
-  <sheetProtection password="DBF4" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection objects="1" password="DBF4" scenarios="1" sheet="1"/>
   <mergeCells count="402">
     <mergeCell ref="V62:Z62"/>
     <mergeCell ref="V63:Z63"/>
@@ -50198,7 +50198,7 @@
       <c r="DF171" s="29"/>
     </row>
   </sheetData>
-  <sheetProtection password="DBF4" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection objects="1" password="DBF4" scenarios="1" sheet="1"/>
   <mergeCells count="135">
     <mergeCell ref="CF22:CY25"/>
     <mergeCell ref="AO29:AX30"/>
@@ -56343,7 +56343,7 @@
       <c r="BC84" s="28"/>
     </row>
   </sheetData>
-  <sheetProtection password="DBF4" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection objects="1" password="DBF4" scenarios="1" sheet="1"/>
   <mergeCells count="402">
     <mergeCell ref="AE13:AP13"/>
     <mergeCell ref="AR13:AU13"/>
